--- a/nail_artist_forms/007_nail_shape_customization_feedback_survey--nail_artist_forms.xlsx
+++ b/nail_artist_forms/007_nail_shape_customization_feedback_survey--nail_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'curved'}</t>
+          <t>curved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Curved'}</t>
+          <t>Curved</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'round'}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Round'}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'squared'}</t>
+          <t>squared</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Squared'}</t>
+          <t>Squared</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'oval'}</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Oval'}</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'almond'}</t>
+          <t>almond</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Almond'}</t>
+          <t>Almond</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'nail_extensions'}</t>
+          <t>nail_extensions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Nail extensions'}</t>
+          <t>Nail extensions</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'nail_art'}</t>
+          <t>nail_art</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Nail art'}</t>
+          <t>Nail art</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'nail_shaping'}</t>
+          <t>nail_shaping</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Nail shaping'}</t>
+          <t>Nail shaping</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'nail_polishing'}</t>
+          <t>nail_polishing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Nail polishing'}</t>
+          <t>Nail polishing</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'nail_shaping'}</t>
+          <t>manicure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Nail shaping'}</t>
+          <t>Manicure</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'manicure'}</t>
+          <t>pedicure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Manicure'}</t>
+          <t>Pedicure</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'pedicure'}</t>
+          <t>waxing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Pedicure'}</t>
+          <t>Waxing</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'waxing'}</t>
+          <t>brow_shaping</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Waxing'}</t>
+          <t>Brow shaping</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'brow_shaping'}</t>
+          <t>lash_services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Brow shaping'}</t>
+          <t>Lash services</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>new_services_choices</t>
+          <t>nail_shape_satisfaction_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'lash_services'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Lash services'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nail_shape_satisfaction_choices</t>
+          <t>service_satisfaction_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>service_satisfaction_choices</t>
+          <t>nail_shape_customization_satisfaction_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nail_shape_customization_satisfaction_choices</t>
+          <t>nail_shape_customization_service_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>nail_shaping</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Nail shaping</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'nail_shaping'}</t>
+          <t>nail_polishing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Nail shaping'}</t>
+          <t>Nail polishing</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'nail_polishing'}</t>
+          <t>waxing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Nail polishing'}</t>
+          <t>Waxing</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'waxing'}</t>
+          <t>brow_shaping</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Waxing'}</t>
+          <t>Brow shaping</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'brow_shaping'}</t>
+          <t>lash_services</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Brow shaping'}</t>
+          <t>Lash services</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'lash_services'}</t>
+          <t>manicure</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Lash services'}</t>
+          <t>Manicure</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'manicure'}</t>
+          <t>pedicure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Manicure'}</t>
+          <t>Pedicure</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nail_shape_customization_service_choices</t>
+          <t>nail_shape_customization_salon_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'pedicure'}</t>
+          <t>local_salon</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Pedicure'}</t>
+          <t>Local salon</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'local_salon'}</t>
+          <t>chain_salon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Local salon'}</t>
+          <t>Chain salon</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'chain_salon'}</t>
+          <t>mobile_salon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Chain salon'}</t>
+          <t>Mobile salon</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_salon'}</t>
+          <t>online_salon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile salon'}</t>
+          <t>Online salon</t>
         </is>
       </c>
     </row>
@@ -1998,29 +1998,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'online_salon'}</t>
+          <t>home_service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Online salon'}</t>
+          <t>Home service</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nail_shape_customization_salon_choices</t>
+          <t>nail_shape_customization_new_services_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'home_service'}</t>
+          <t>nail_extensions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Home service'}</t>
+          <t>Nail extensions</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'nail_extensions'}</t>
+          <t>nail_art</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Nail extensions'}</t>
+          <t>Nail art</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'nail_art'}</t>
+          <t>gel_and_acrylic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Nail art'}</t>
+          <t>Gel and acrylic</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'gel_and_acrylic'}</t>
+          <t>shellac_and_gel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Gel and acrylic'}</t>
+          <t>Shellac and gel</t>
         </is>
       </c>
     </row>
@@ -2083,29 +2083,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'shellac_and_gel'}</t>
+          <t>nail_shaping</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Shellac and gel'}</t>
+          <t>Nail shaping</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nail_shape_customization_new_services_choices</t>
+          <t>client_satisfaction_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'nail_shaping'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Nail shaping'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2168,29 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>client_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>{'label':_'very_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
